--- a/pages/video_analysis/WTS_Master_Women.xlsx
+++ b/pages/video_analysis/WTS_Master_Women.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D9C711-F2EE-4D74-B097-788F710A518E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB26B42-DD84-4D3F-B060-E89EF25F6C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3254" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3273" uniqueCount="164">
   <si>
     <t>Title</t>
   </si>
@@ -456,6 +456,63 @@
   <si>
     <t>https://youtu.be/A9RPvQhy2kA</t>
   </si>
+  <si>
+    <t>https://youtu.be/5Xeup-WDQ3Q</t>
+  </si>
+  <si>
+    <t>https://youtu.be/LBTBDSO7xoY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/hKc0hARjwVo</t>
+  </si>
+  <si>
+    <t>https://youtu.be/qyCKvuoJjHc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/1iSEJ76x7NM</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Rb7YZngU_ww</t>
+  </si>
+  <si>
+    <t>https://youtu.be/2Ebr219Ql_c</t>
+  </si>
+  <si>
+    <t>https://youtu.be/BN07O7o7MIY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/_OkDGtb68ec</t>
+  </si>
+  <si>
+    <t>https://youtu.be/9CIdlIXj4nk</t>
+  </si>
+  <si>
+    <t>https://youtu.be/flnexX005_g</t>
+  </si>
+  <si>
+    <t>https://youtu.be/F8YpAAV3rXc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/WCfI6Qdb7Ls</t>
+  </si>
+  <si>
+    <t>https://youtu.be/bTXtMPA30vI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/JYUc8zUq7h4</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ij-ZJIPiLYA</t>
+  </si>
+  <si>
+    <t>https://youtu.be/IVduiHY6-SU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Em_8hXoCAtI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/v7bg4ng8D38</t>
+  </si>
 </sst>
 </file>
 
@@ -17834,7 +17891,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="977" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="977" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A977" t="s">
         <v>42</v>
       </c>
@@ -17851,7 +17908,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="978" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="978" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A978" t="s">
         <v>42</v>
       </c>
@@ -17868,7 +17925,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="979" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="979" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A979" t="s">
         <v>42</v>
       </c>
@@ -17885,7 +17942,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="980" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="980" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A980" t="s">
         <v>42</v>
       </c>
@@ -17902,7 +17959,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="981" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="981" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A981" t="s">
         <v>42</v>
       </c>
@@ -17919,7 +17976,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="982" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="982" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A982" t="s">
         <v>43</v>
       </c>
@@ -17938,8 +17995,11 @@
       <c r="F982" s="2">
         <v>45386</v>
       </c>
-    </row>
-    <row r="983" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G982" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="983" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A983" t="s">
         <v>43</v>
       </c>
@@ -17959,7 +18019,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="984" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="984" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A984" t="s">
         <v>43</v>
       </c>
@@ -17979,7 +18039,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="985" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="985" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A985" t="s">
         <v>43</v>
       </c>
@@ -17996,7 +18056,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="986" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="986" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A986" t="s">
         <v>43</v>
       </c>
@@ -18013,7 +18073,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="987" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="987" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A987" t="s">
         <v>43</v>
       </c>
@@ -18030,7 +18090,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="988" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="988" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A988" t="s">
         <v>43</v>
       </c>
@@ -18047,7 +18107,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="989" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="989" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A989" t="s">
         <v>43</v>
       </c>
@@ -18064,7 +18124,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="990" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="990" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A990" t="s">
         <v>43</v>
       </c>
@@ -18081,7 +18141,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="991" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="991" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A991" t="s">
         <v>43</v>
       </c>
@@ -18098,7 +18158,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="992" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="992" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A992" t="s">
         <v>43</v>
       </c>
@@ -18387,7 +18447,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1009" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1009" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1009" t="s">
         <v>43</v>
       </c>
@@ -18404,7 +18464,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1010" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1010" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1010" t="s">
         <v>44</v>
       </c>
@@ -18423,8 +18483,11 @@
       <c r="F1010" s="2">
         <v>45386</v>
       </c>
-    </row>
-    <row r="1011" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1010" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1011" t="s">
         <v>44</v>
       </c>
@@ -18444,7 +18507,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1012" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1012" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1012" t="s">
         <v>44</v>
       </c>
@@ -18464,7 +18527,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1013" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1013" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1013" t="s">
         <v>44</v>
       </c>
@@ -18481,7 +18544,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1014" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1014" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1014" t="s">
         <v>44</v>
       </c>
@@ -18498,7 +18561,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1015" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1015" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1015" t="s">
         <v>44</v>
       </c>
@@ -18515,7 +18578,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1016" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1016" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1016" t="s">
         <v>44</v>
       </c>
@@ -18532,7 +18595,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1017" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1017" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1017" t="s">
         <v>44</v>
       </c>
@@ -18549,7 +18612,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1018" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1018" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1018" t="s">
         <v>44</v>
       </c>
@@ -18566,7 +18629,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1019" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1019" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1019" t="s">
         <v>44</v>
       </c>
@@ -18583,7 +18646,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1020" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1020" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1020" t="s">
         <v>44</v>
       </c>
@@ -18600,7 +18663,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1021" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1021" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1021" t="s">
         <v>44</v>
       </c>
@@ -18617,7 +18680,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1022" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1022" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1022" t="s">
         <v>44</v>
       </c>
@@ -18634,7 +18697,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1023" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1023" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1023" t="s">
         <v>44</v>
       </c>
@@ -18651,7 +18714,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1024" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1024" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1024" t="s">
         <v>44</v>
       </c>
@@ -18668,7 +18731,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1025" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1025" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1025" t="s">
         <v>44</v>
       </c>
@@ -18685,7 +18748,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1026" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1026" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1026" t="s">
         <v>44</v>
       </c>
@@ -18702,7 +18765,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1027" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1027" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1027" t="s">
         <v>44</v>
       </c>
@@ -18719,7 +18782,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1028" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1028" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1028" t="s">
         <v>44</v>
       </c>
@@ -18736,7 +18799,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1029" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1029" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1029" t="s">
         <v>44</v>
       </c>
@@ -18753,7 +18816,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1030" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1030" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1030" t="s">
         <v>44</v>
       </c>
@@ -18770,7 +18833,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1031" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1031" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1031" t="s">
         <v>44</v>
       </c>
@@ -18787,7 +18850,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1032" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1032" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1032" t="s">
         <v>44</v>
       </c>
@@ -18804,7 +18867,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1033" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1033" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1033" t="s">
         <v>44</v>
       </c>
@@ -18821,7 +18884,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1034" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1034" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1034" t="s">
         <v>44</v>
       </c>
@@ -18838,7 +18901,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1035" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1035" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1035" t="s">
         <v>44</v>
       </c>
@@ -18855,7 +18918,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1036" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1036" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1036" t="s">
         <v>44</v>
       </c>
@@ -18872,7 +18935,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1037" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1037" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1037" t="s">
         <v>44</v>
       </c>
@@ -18889,7 +18952,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1038" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1038" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1038" t="s">
         <v>45</v>
       </c>
@@ -18908,8 +18971,11 @@
       <c r="F1038" s="2">
         <v>45386</v>
       </c>
-    </row>
-    <row r="1039" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1038" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1039" t="s">
         <v>45</v>
       </c>
@@ -18929,7 +18995,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1040" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1040" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1040" t="s">
         <v>45</v>
       </c>
@@ -19221,7 +19287,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1057" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1057" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1057" t="s">
         <v>45</v>
       </c>
@@ -19238,7 +19304,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1058" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1058" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1058" t="s">
         <v>45</v>
       </c>
@@ -19255,7 +19321,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1059" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1059" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1059" t="s">
         <v>45</v>
       </c>
@@ -19272,7 +19338,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1060" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1060" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1060" t="s">
         <v>45</v>
       </c>
@@ -19289,7 +19355,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1061" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1061" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1061" t="s">
         <v>45</v>
       </c>
@@ -19306,7 +19372,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1062" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1062" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1062" t="s">
         <v>45</v>
       </c>
@@ -19323,7 +19389,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1063" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1063" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1063" t="s">
         <v>45</v>
       </c>
@@ -19340,7 +19406,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1064" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1064" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1064" t="s">
         <v>45</v>
       </c>
@@ -19357,7 +19423,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1065" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1065" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1065" t="s">
         <v>45</v>
       </c>
@@ -19374,7 +19440,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1066" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1066" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1066" t="s">
         <v>46</v>
       </c>
@@ -19393,8 +19459,11 @@
       <c r="F1066" s="2">
         <v>45386</v>
       </c>
-    </row>
-    <row r="1067" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1066" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1067" t="s">
         <v>46</v>
       </c>
@@ -19414,7 +19483,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1068" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1068" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1068" t="s">
         <v>46</v>
       </c>
@@ -19434,7 +19503,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1069" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1069" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1069" t="s">
         <v>46</v>
       </c>
@@ -19451,7 +19520,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1070" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1070" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1070" t="s">
         <v>46</v>
       </c>
@@ -19468,7 +19537,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1071" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1071" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1071" t="s">
         <v>46</v>
       </c>
@@ -19485,7 +19554,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1072" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1072" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1072" t="s">
         <v>46</v>
       </c>
@@ -19774,7 +19843,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1089" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1089" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1089" t="s">
         <v>46</v>
       </c>
@@ -19791,7 +19860,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1090" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1090" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1090" t="s">
         <v>46</v>
       </c>
@@ -19808,7 +19877,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1091" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1091" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1091" t="s">
         <v>46</v>
       </c>
@@ -19825,7 +19894,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1092" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1092" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1092" t="s">
         <v>46</v>
       </c>
@@ -19842,7 +19911,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1093" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1093" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1093" t="s">
         <v>46</v>
       </c>
@@ -19859,7 +19928,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="1094" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1094" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1094" t="s">
         <v>47</v>
       </c>
@@ -19875,8 +19944,11 @@
       <c r="F1094" s="2">
         <v>45387</v>
       </c>
-    </row>
-    <row r="1095" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1094" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1095" t="s">
         <v>47</v>
       </c>
@@ -19893,7 +19965,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1096" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1096" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1096" t="s">
         <v>47</v>
       </c>
@@ -19910,7 +19982,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1097" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1097" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1097" t="s">
         <v>47</v>
       </c>
@@ -19927,7 +19999,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1098" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1098" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1098" t="s">
         <v>47</v>
       </c>
@@ -19944,7 +20016,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1099" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1099" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1099" t="s">
         <v>47</v>
       </c>
@@ -19961,7 +20033,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1100" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1100" t="s">
         <v>47</v>
       </c>
@@ -19978,7 +20050,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1101" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1101" t="s">
         <v>47</v>
       </c>
@@ -19995,7 +20067,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1102" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1102" t="s">
         <v>47</v>
       </c>
@@ -20012,7 +20084,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1103" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1103" t="s">
         <v>47</v>
       </c>
@@ -20029,7 +20101,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1104" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1104" t="s">
         <v>47</v>
       </c>
@@ -20318,7 +20390,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1121" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1121" t="s">
         <v>47</v>
       </c>
@@ -20335,7 +20407,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1122" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1122" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1122" t="s">
         <v>48</v>
       </c>
@@ -20351,8 +20423,11 @@
       <c r="F1122" s="2">
         <v>45387</v>
       </c>
-    </row>
-    <row r="1123" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1122" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1123" t="s">
         <v>48</v>
       </c>
@@ -20369,7 +20444,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1124" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1124" t="s">
         <v>48</v>
       </c>
@@ -20386,7 +20461,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1125" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1125" t="s">
         <v>48</v>
       </c>
@@ -20403,7 +20478,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1126" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1126" t="s">
         <v>48</v>
       </c>
@@ -20420,7 +20495,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1127" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1127" t="s">
         <v>48</v>
       </c>
@@ -20437,7 +20512,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1128" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1128" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1128" t="s">
         <v>48</v>
       </c>
@@ -20454,7 +20529,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1129" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1129" t="s">
         <v>48</v>
       </c>
@@ -20471,7 +20546,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1130" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1130" t="s">
         <v>48</v>
       </c>
@@ -20488,7 +20563,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1131" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1131" t="s">
         <v>48</v>
       </c>
@@ -20505,7 +20580,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1132" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1132" t="s">
         <v>48</v>
       </c>
@@ -20522,7 +20597,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1133" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1133" t="s">
         <v>48</v>
       </c>
@@ -20539,7 +20614,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1134" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1134" t="s">
         <v>48</v>
       </c>
@@ -20556,7 +20631,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1135" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1135" t="s">
         <v>48</v>
       </c>
@@ -20573,7 +20648,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1136" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1136" t="s">
         <v>48</v>
       </c>
@@ -20590,7 +20665,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1137" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1137" t="s">
         <v>48</v>
       </c>
@@ -20607,7 +20682,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1138" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1138" t="s">
         <v>48</v>
       </c>
@@ -20624,7 +20699,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1139" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1139" t="s">
         <v>48</v>
       </c>
@@ -20641,7 +20716,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1140" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1140" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1140" t="s">
         <v>48</v>
       </c>
@@ -20658,7 +20733,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1141" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1141" t="s">
         <v>48</v>
       </c>
@@ -20675,7 +20750,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1142" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1142" t="s">
         <v>48</v>
       </c>
@@ -20692,7 +20767,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1143" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1143" t="s">
         <v>48</v>
       </c>
@@ -20709,7 +20784,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1144" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1144" t="s">
         <v>48</v>
       </c>
@@ -20726,7 +20801,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1145" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1145" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1145" t="s">
         <v>48</v>
       </c>
@@ -20743,7 +20818,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1146" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1146" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1146" t="s">
         <v>48</v>
       </c>
@@ -20760,7 +20835,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1147" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1147" t="s">
         <v>48</v>
       </c>
@@ -20777,7 +20852,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1148" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1148" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1148" t="s">
         <v>48</v>
       </c>
@@ -20794,7 +20869,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1149" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1149" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1149" t="s">
         <v>48</v>
       </c>
@@ -20811,7 +20886,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1150" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1150" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1150" t="s">
         <v>49</v>
       </c>
@@ -20827,8 +20902,11 @@
       <c r="F1150" s="2">
         <v>45387</v>
       </c>
-    </row>
-    <row r="1151" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1150" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1151" t="s">
         <v>49</v>
       </c>
@@ -20845,7 +20923,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1152" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1152" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1152" t="s">
         <v>49</v>
       </c>
@@ -21134,7 +21212,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1169" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1169" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1169" t="s">
         <v>49</v>
       </c>
@@ -21151,7 +21229,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1170" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1170" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1170" t="s">
         <v>49</v>
       </c>
@@ -21168,7 +21246,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1171" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1171" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1171" t="s">
         <v>49</v>
       </c>
@@ -21185,7 +21263,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1172" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1172" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1172" t="s">
         <v>49</v>
       </c>
@@ -21202,7 +21280,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1173" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1173" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1173" t="s">
         <v>49</v>
       </c>
@@ -21219,7 +21297,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1174" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1174" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1174" t="s">
         <v>49</v>
       </c>
@@ -21236,7 +21314,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1175" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1175" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1175" t="s">
         <v>49</v>
       </c>
@@ -21253,7 +21331,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1176" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1176" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1176" t="s">
         <v>49</v>
       </c>
@@ -21270,7 +21348,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1177" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1177" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1177" t="s">
         <v>49</v>
       </c>
@@ -21287,7 +21365,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1178" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1178" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1178" t="s">
         <v>50</v>
       </c>
@@ -21303,8 +21381,11 @@
       <c r="F1178" s="2">
         <v>45387</v>
       </c>
-    </row>
-    <row r="1179" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1178" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1179" t="s">
         <v>50</v>
       </c>
@@ -21321,7 +21402,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1180" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1180" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1180" t="s">
         <v>50</v>
       </c>
@@ -21338,7 +21419,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1181" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1181" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1181" t="s">
         <v>50</v>
       </c>
@@ -21355,7 +21436,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1182" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1182" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1182" t="s">
         <v>50</v>
       </c>
@@ -21372,7 +21453,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1183" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1183" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1183" t="s">
         <v>50</v>
       </c>
@@ -21389,7 +21470,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1184" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1184" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1184" t="s">
         <v>50</v>
       </c>
@@ -21678,7 +21759,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1201" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1201" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1201" t="s">
         <v>50</v>
       </c>
@@ -21695,7 +21776,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1202" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1202" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1202" t="s">
         <v>50</v>
       </c>
@@ -21712,7 +21793,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1203" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1203" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1203" t="s">
         <v>50</v>
       </c>
@@ -21729,7 +21810,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1204" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1204" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1204" t="s">
         <v>50</v>
       </c>
@@ -21746,7 +21827,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1205" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1205" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1205" t="s">
         <v>50</v>
       </c>
@@ -21763,7 +21844,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1206" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1206" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1206" t="s">
         <v>51</v>
       </c>
@@ -21779,8 +21860,11 @@
       <c r="F1206" s="2">
         <v>45387</v>
       </c>
-    </row>
-    <row r="1207" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1206" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1207" t="s">
         <v>51</v>
       </c>
@@ -21797,7 +21881,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1208" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1208" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1208" t="s">
         <v>51</v>
       </c>
@@ -21814,7 +21898,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1209" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1209" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1209" t="s">
         <v>51</v>
       </c>
@@ -21831,7 +21915,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1210" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1210" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1210" t="s">
         <v>51</v>
       </c>
@@ -21848,7 +21932,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1211" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1211" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1211" t="s">
         <v>51</v>
       </c>
@@ -21865,7 +21949,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1212" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1212" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1212" t="s">
         <v>51</v>
       </c>
@@ -21882,7 +21966,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1213" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1213" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1213" t="s">
         <v>51</v>
       </c>
@@ -21899,7 +21983,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1214" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1214" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1214" t="s">
         <v>51</v>
       </c>
@@ -21916,7 +22000,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1215" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1215" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1215" t="s">
         <v>51</v>
       </c>
@@ -21933,7 +22017,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1216" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1216" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1216" t="s">
         <v>51</v>
       </c>
@@ -22222,7 +22306,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1233" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1233" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1233" t="s">
         <v>51</v>
       </c>
@@ -22239,7 +22323,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1234" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1234" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1234" t="s">
         <v>52</v>
       </c>
@@ -22255,8 +22339,11 @@
       <c r="F1234" s="2">
         <v>45387</v>
       </c>
-    </row>
-    <row r="1235" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1234" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1235" t="s">
         <v>52</v>
       </c>
@@ -22273,7 +22360,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1236" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1236" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1236" t="s">
         <v>52</v>
       </c>
@@ -22290,7 +22377,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1237" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1237" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1237" t="s">
         <v>52</v>
       </c>
@@ -22307,7 +22394,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1238" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1238" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1238" t="s">
         <v>52</v>
       </c>
@@ -22324,7 +22411,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1239" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1239" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1239" t="s">
         <v>52</v>
       </c>
@@ -22341,7 +22428,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1240" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1240" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1240" t="s">
         <v>52</v>
       </c>
@@ -22358,7 +22445,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1241" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1241" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1241" t="s">
         <v>52</v>
       </c>
@@ -22375,7 +22462,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1242" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1242" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1242" t="s">
         <v>52</v>
       </c>
@@ -22392,7 +22479,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1243" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1243" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1243" t="s">
         <v>52</v>
       </c>
@@ -22409,7 +22496,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1244" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1244" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1244" t="s">
         <v>52</v>
       </c>
@@ -22426,7 +22513,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1245" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1245" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1245" t="s">
         <v>52</v>
       </c>
@@ -22443,7 +22530,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1246" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1246" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1246" t="s">
         <v>52</v>
       </c>
@@ -22460,7 +22547,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1247" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1247" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1247" t="s">
         <v>52</v>
       </c>
@@ -22477,7 +22564,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1248" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1248" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1248" t="s">
         <v>52</v>
       </c>
@@ -22494,7 +22581,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1249" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1249" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1249" t="s">
         <v>52</v>
       </c>
@@ -22511,7 +22598,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1250" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1250" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1250" t="s">
         <v>52</v>
       </c>
@@ -22528,7 +22615,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1251" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1251" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1251" t="s">
         <v>52</v>
       </c>
@@ -22545,7 +22632,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1252" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1252" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1252" t="s">
         <v>52</v>
       </c>
@@ -22562,7 +22649,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1253" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1253" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1253" t="s">
         <v>52</v>
       </c>
@@ -22579,7 +22666,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1254" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1254" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1254" t="s">
         <v>52</v>
       </c>
@@ -22596,7 +22683,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1255" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1255" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1255" t="s">
         <v>52</v>
       </c>
@@ -22613,7 +22700,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1256" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1256" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1256" t="s">
         <v>52</v>
       </c>
@@ -22630,7 +22717,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1257" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1257" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1257" t="s">
         <v>52</v>
       </c>
@@ -22647,7 +22734,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1258" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1258" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1258" t="s">
         <v>52</v>
       </c>
@@ -22664,7 +22751,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1259" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1259" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1259" t="s">
         <v>52</v>
       </c>
@@ -22681,7 +22768,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1260" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1260" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1260" t="s">
         <v>52</v>
       </c>
@@ -22698,7 +22785,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1261" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1261" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1261" t="s">
         <v>52</v>
       </c>
@@ -22715,7 +22802,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1262" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1262" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1262" t="s">
         <v>53</v>
       </c>
@@ -22731,8 +22818,11 @@
       <c r="F1262" s="2">
         <v>45387</v>
       </c>
-    </row>
-    <row r="1263" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1262" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1263" t="s">
         <v>53</v>
       </c>
@@ -22749,7 +22839,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1264" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1264" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1264" t="s">
         <v>53</v>
       </c>
@@ -23038,7 +23128,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1281" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1281" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1281" t="s">
         <v>53</v>
       </c>
@@ -23055,7 +23145,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1282" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1282" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1282" t="s">
         <v>53</v>
       </c>
@@ -23072,7 +23162,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1283" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1283" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1283" t="s">
         <v>53</v>
       </c>
@@ -23089,7 +23179,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1284" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1284" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1284" t="s">
         <v>53</v>
       </c>
@@ -23106,7 +23196,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1285" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1285" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1285" t="s">
         <v>53</v>
       </c>
@@ -23123,7 +23213,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1286" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1286" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1286" t="s">
         <v>53</v>
       </c>
@@ -23140,7 +23230,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1287" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1287" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1287" t="s">
         <v>53</v>
       </c>
@@ -23157,7 +23247,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1288" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1288" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1288" t="s">
         <v>53</v>
       </c>
@@ -23174,7 +23264,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1289" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1289" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1289" t="s">
         <v>53</v>
       </c>
@@ -23191,7 +23281,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1290" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1290" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1290" t="s">
         <v>54</v>
       </c>
@@ -23207,8 +23297,11 @@
       <c r="F1290" s="2">
         <v>45387</v>
       </c>
-    </row>
-    <row r="1291" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1290" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1291" t="s">
         <v>54</v>
       </c>
@@ -23225,7 +23318,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1292" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1292" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1292" t="s">
         <v>54</v>
       </c>
@@ -23242,7 +23335,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1293" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1293" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1293" t="s">
         <v>54</v>
       </c>
@@ -23259,7 +23352,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1294" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1294" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1294" t="s">
         <v>54</v>
       </c>
@@ -23276,7 +23369,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1295" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1295" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1295" t="s">
         <v>54</v>
       </c>
@@ -23293,7 +23386,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1296" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1296" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1296" t="s">
         <v>54</v>
       </c>
@@ -23582,7 +23675,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1313" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1313" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1313" t="s">
         <v>54</v>
       </c>
@@ -23599,7 +23692,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1314" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1314" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1314" t="s">
         <v>54</v>
       </c>
@@ -23616,7 +23709,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1315" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1315" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1315" t="s">
         <v>54</v>
       </c>
@@ -23633,7 +23726,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1316" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1316" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1316" t="s">
         <v>54</v>
       </c>
@@ -23650,7 +23743,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1317" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1317" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1317" t="s">
         <v>54</v>
       </c>
@@ -23667,7 +23760,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1318" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1318" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1318" t="s">
         <v>55</v>
       </c>
@@ -23683,8 +23776,11 @@
       <c r="F1318" s="2">
         <v>45387</v>
       </c>
-    </row>
-    <row r="1319" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1318" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1319" t="s">
         <v>55</v>
       </c>
@@ -23701,7 +23797,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1320" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1320" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1320" t="s">
         <v>55</v>
       </c>
@@ -23718,7 +23814,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1321" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1321" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1321" t="s">
         <v>55</v>
       </c>
@@ -23735,7 +23831,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1322" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1322" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1322" t="s">
         <v>55</v>
       </c>
@@ -23752,7 +23848,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1323" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1323" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1323" t="s">
         <v>55</v>
       </c>
@@ -23769,7 +23865,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1324" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1324" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1324" t="s">
         <v>55</v>
       </c>
@@ -23786,7 +23882,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1325" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1325" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1325" t="s">
         <v>55</v>
       </c>
@@ -23803,7 +23899,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1326" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1326" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1326" t="s">
         <v>55</v>
       </c>
@@ -23820,7 +23916,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1327" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1327" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1327" t="s">
         <v>55</v>
       </c>
@@ -23837,7 +23933,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1328" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1328" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1328" t="s">
         <v>55</v>
       </c>
@@ -24126,7 +24222,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1345" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1345" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1345" t="s">
         <v>55</v>
       </c>
@@ -24143,7 +24239,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1346" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1346" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1346" t="s">
         <v>56</v>
       </c>
@@ -24159,8 +24255,11 @@
       <c r="F1346" s="2">
         <v>45387</v>
       </c>
-    </row>
-    <row r="1347" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1346" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1347" t="s">
         <v>56</v>
       </c>
@@ -24177,7 +24276,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1348" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1348" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1348" t="s">
         <v>56</v>
       </c>
@@ -24194,7 +24293,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1349" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1349" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1349" t="s">
         <v>56</v>
       </c>
@@ -24211,7 +24310,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1350" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1350" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1350" t="s">
         <v>56</v>
       </c>
@@ -24228,7 +24327,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1351" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1351" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1351" t="s">
         <v>56</v>
       </c>
@@ -24245,7 +24344,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1352" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1352" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1352" t="s">
         <v>56</v>
       </c>
@@ -24262,7 +24361,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1353" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1353" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1353" t="s">
         <v>56</v>
       </c>
@@ -24279,7 +24378,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1354" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1354" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1354" t="s">
         <v>56</v>
       </c>
@@ -24296,7 +24395,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1355" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1355" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1355" t="s">
         <v>56</v>
       </c>
@@ -24313,7 +24412,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1356" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1356" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1356" t="s">
         <v>56</v>
       </c>
@@ -24330,7 +24429,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1357" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1357" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1357" t="s">
         <v>56</v>
       </c>
@@ -24347,7 +24446,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1358" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1358" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1358" t="s">
         <v>56</v>
       </c>
@@ -24364,7 +24463,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1359" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1359" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1359" t="s">
         <v>56</v>
       </c>
@@ -24381,7 +24480,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1360" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1360" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1360" t="s">
         <v>56</v>
       </c>
@@ -24398,7 +24497,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1361" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1361" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1361" t="s">
         <v>56</v>
       </c>
@@ -24415,7 +24514,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1362" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1362" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1362" t="s">
         <v>56</v>
       </c>
@@ -24432,7 +24531,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1363" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1363" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1363" t="s">
         <v>56</v>
       </c>
@@ -24449,7 +24548,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1364" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1364" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1364" t="s">
         <v>56</v>
       </c>
@@ -24466,7 +24565,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1365" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1365" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1365" t="s">
         <v>56</v>
       </c>
@@ -24483,7 +24582,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1366" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1366" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1366" t="s">
         <v>56</v>
       </c>
@@ -24500,7 +24599,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1367" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1367" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1367" t="s">
         <v>56</v>
       </c>
@@ -24517,7 +24616,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1368" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1368" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1368" t="s">
         <v>56</v>
       </c>
@@ -24534,7 +24633,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1369" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1369" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1369" t="s">
         <v>56</v>
       </c>
@@ -24551,7 +24650,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1370" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1370" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1370" t="s">
         <v>56</v>
       </c>
@@ -24568,7 +24667,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1371" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1371" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1371" t="s">
         <v>56</v>
       </c>
@@ -24585,7 +24684,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1372" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1372" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1372" t="s">
         <v>56</v>
       </c>
@@ -24602,7 +24701,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1373" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1373" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1373" t="s">
         <v>56</v>
       </c>
@@ -24619,7 +24718,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1374" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1374" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1374" t="s">
         <v>57</v>
       </c>
@@ -24635,8 +24734,11 @@
       <c r="F1374" s="2">
         <v>45387</v>
       </c>
-    </row>
-    <row r="1375" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1374" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1375" t="s">
         <v>57</v>
       </c>
@@ -24653,7 +24755,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1376" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1376" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1376" t="s">
         <v>57</v>
       </c>
@@ -24942,7 +25044,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1393" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1393" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1393" t="s">
         <v>57</v>
       </c>
@@ -24959,7 +25061,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1394" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1394" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1394" t="s">
         <v>57</v>
       </c>
@@ -24976,7 +25078,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1395" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1395" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1395" t="s">
         <v>57</v>
       </c>
@@ -24993,7 +25095,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1396" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1396" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1396" t="s">
         <v>57</v>
       </c>
@@ -25010,7 +25112,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1397" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1397" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1397" t="s">
         <v>57</v>
       </c>
@@ -25027,7 +25129,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1398" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1398" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1398" t="s">
         <v>57</v>
       </c>
@@ -25044,7 +25146,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1399" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1399" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1399" t="s">
         <v>57</v>
       </c>
@@ -25061,7 +25163,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1400" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1400" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1400" t="s">
         <v>57</v>
       </c>
@@ -25078,7 +25180,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1401" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1401" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1401" t="s">
         <v>57</v>
       </c>
@@ -25095,7 +25197,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1402" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1402" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1402" t="s">
         <v>58</v>
       </c>
@@ -25111,8 +25213,11 @@
       <c r="F1402" s="2">
         <v>45387</v>
       </c>
-    </row>
-    <row r="1403" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1402" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1403" t="s">
         <v>58</v>
       </c>
@@ -25129,7 +25234,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1404" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1404" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1404" t="s">
         <v>58</v>
       </c>
@@ -25146,7 +25251,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1405" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1405" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1405" t="s">
         <v>58</v>
       </c>
@@ -25163,7 +25268,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1406" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1406" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1406" t="s">
         <v>58</v>
       </c>
@@ -25180,7 +25285,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1407" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1407" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1407" t="s">
         <v>58</v>
       </c>
@@ -25197,7 +25302,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1408" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1408" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1408" t="s">
         <v>58</v>
       </c>
@@ -25486,7 +25591,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1425" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1425" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1425" t="s">
         <v>58</v>
       </c>
@@ -25503,7 +25608,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1426" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1426" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1426" t="s">
         <v>58</v>
       </c>
@@ -25520,7 +25625,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1427" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1427" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1427" t="s">
         <v>58</v>
       </c>
@@ -25537,7 +25642,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1428" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1428" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1428" t="s">
         <v>58</v>
       </c>
@@ -25554,7 +25659,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1429" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1429" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1429" t="s">
         <v>58</v>
       </c>
@@ -25571,7 +25676,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1430" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1430" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1430" t="s">
         <v>59</v>
       </c>
@@ -25587,8 +25692,11 @@
       <c r="F1430" s="2">
         <v>45387</v>
       </c>
-    </row>
-    <row r="1431" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1430" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1431" t="s">
         <v>59</v>
       </c>
@@ -25605,7 +25713,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1432" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1432" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1432" t="s">
         <v>59</v>
       </c>
@@ -25622,7 +25730,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1433" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1433" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1433" t="s">
         <v>59</v>
       </c>
@@ -25639,7 +25747,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1434" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1434" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1434" t="s">
         <v>59</v>
       </c>
@@ -25656,7 +25764,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1435" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1435" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1435" t="s">
         <v>59</v>
       </c>
@@ -25673,7 +25781,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1436" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1436" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1436" t="s">
         <v>59</v>
       </c>
@@ -25690,7 +25798,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1437" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1437" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1437" t="s">
         <v>59</v>
       </c>
@@ -25707,7 +25815,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1438" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1438" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1438" t="s">
         <v>59</v>
       </c>
@@ -25724,7 +25832,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1439" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1439" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1439" t="s">
         <v>59</v>
       </c>
@@ -25741,7 +25849,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1440" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1440" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1440" t="s">
         <v>59</v>
       </c>
@@ -26030,7 +26138,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1457" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1457" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1457" t="s">
         <v>59</v>
       </c>
@@ -26047,7 +26155,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1458" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1458" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1458" t="s">
         <v>60</v>
       </c>
@@ -26063,8 +26171,11 @@
       <c r="F1458" s="2">
         <v>45387</v>
       </c>
-    </row>
-    <row r="1459" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1458" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1459" t="s">
         <v>60</v>
       </c>
@@ -26081,7 +26192,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1460" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1460" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1460" t="s">
         <v>60</v>
       </c>
@@ -26098,7 +26209,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1461" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1461" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1461" t="s">
         <v>60</v>
       </c>
@@ -26115,7 +26226,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1462" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1462" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1462" t="s">
         <v>60</v>
       </c>
@@ -26132,7 +26243,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1463" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1463" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1463" t="s">
         <v>60</v>
       </c>
@@ -26149,7 +26260,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1464" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1464" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1464" t="s">
         <v>60</v>
       </c>
@@ -26166,7 +26277,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1465" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1465" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1465" t="s">
         <v>60</v>
       </c>
@@ -26183,7 +26294,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1466" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1466" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1466" t="s">
         <v>60</v>
       </c>
@@ -26200,7 +26311,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1467" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1467" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1467" t="s">
         <v>60</v>
       </c>
@@ -26217,7 +26328,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1468" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1468" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1468" t="s">
         <v>60</v>
       </c>
@@ -26234,7 +26345,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1469" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1469" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1469" t="s">
         <v>60</v>
       </c>
@@ -26251,7 +26362,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1470" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1470" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1470" t="s">
         <v>60</v>
       </c>
@@ -26268,7 +26379,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1471" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1471" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1471" t="s">
         <v>60</v>
       </c>
@@ -26285,7 +26396,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1472" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1472" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1472" t="s">
         <v>60</v>
       </c>
@@ -26302,7 +26413,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1473" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1473" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1473" t="s">
         <v>60</v>
       </c>
@@ -26319,7 +26430,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1474" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1474" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1474" t="s">
         <v>60</v>
       </c>
@@ -26336,7 +26447,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1475" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1475" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1475" t="s">
         <v>60</v>
       </c>
@@ -26353,7 +26464,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1476" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1476" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1476" t="s">
         <v>60</v>
       </c>
@@ -26370,7 +26481,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1477" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1477" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1477" t="s">
         <v>60</v>
       </c>
@@ -26387,7 +26498,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1478" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1478" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1478" t="s">
         <v>60</v>
       </c>
@@ -26404,7 +26515,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1479" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1479" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1479" t="s">
         <v>60</v>
       </c>
@@ -26421,7 +26532,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1480" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1480" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1480" t="s">
         <v>60</v>
       </c>
@@ -26438,7 +26549,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1481" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1481" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1481" t="s">
         <v>60</v>
       </c>
@@ -26455,7 +26566,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1482" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1482" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1482" t="s">
         <v>60</v>
       </c>
@@ -26472,7 +26583,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1483" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1483" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1483" t="s">
         <v>60</v>
       </c>
@@ -26489,7 +26600,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1484" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1484" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1484" t="s">
         <v>60</v>
       </c>
@@ -26506,7 +26617,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1485" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1485" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1485" t="s">
         <v>60</v>
       </c>
@@ -26523,7 +26634,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1486" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1486" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1486" t="s">
         <v>61</v>
       </c>
@@ -26539,8 +26650,11 @@
       <c r="F1486" s="2">
         <v>45387</v>
       </c>
-    </row>
-    <row r="1487" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1486" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1487" t="s">
         <v>61</v>
       </c>
@@ -26557,7 +26671,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="1488" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1488" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1488" t="s">
         <v>61</v>
       </c>

--- a/pages/video_analysis/WTS_Master_Women.xlsx
+++ b/pages/video_analysis/WTS_Master_Women.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7627544B-04F2-4760-B6F0-8C0EFE8DD085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19EB20D-8236-41FB-96F9-838977BB5FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$1625</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3515" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3515" uniqueCount="167">
   <si>
     <t>Title</t>
   </si>
@@ -232,9 +235,6 @@
     <t>Marker</t>
   </si>
   <si>
-    <t>KOUMAI Taky Marie-Divine</t>
-  </si>
-  <si>
     <t>MICHAUX Julie</t>
   </si>
   <si>
@@ -289,16 +289,7 @@
     <t>PETCH Rebecca</t>
   </si>
   <si>
-    <t>FULTON Shaane Hazel</t>
-  </si>
-  <si>
     <t>ANDREWS Ellesse</t>
-  </si>
-  <si>
-    <t>KARWACKA Marle</t>
-  </si>
-  <si>
-    <t>LOS Urszula</t>
   </si>
   <si>
     <t>SIBIAK Nikola</t>
@@ -334,12 +325,6 @@
     <t>JIANG Yulu</t>
   </si>
   <si>
-    <t>SALAZAR Valles</t>
-  </si>
-  <si>
-    <t>GAXIOLA Gonzalez</t>
-  </si>
-  <si>
     <t>VERDUGO Osuna Yuli</t>
   </si>
   <si>
@@ -349,16 +334,10 @@
     <t>LOS Urzula</t>
   </si>
   <si>
-    <t>GRABOSCH Paulina</t>
-  </si>
-  <si>
     <t>LAMBERINK Hetty</t>
   </si>
   <si>
     <t>KOUAME Taky Marie-Divine</t>
-  </si>
-  <si>
-    <t>FULTON Shanne</t>
   </si>
   <si>
     <t>NA</t>
@@ -975,7 +954,7 @@
         <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="E2">
         <v>114.35</v>
@@ -984,7 +963,7 @@
         <v>45218</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
@@ -998,7 +977,7 @@
         <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3">
         <v>112.5</v>
@@ -1018,7 +997,7 @@
         <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E4">
         <v>116.44</v>
@@ -1463,7 +1442,7 @@
         <v>65</v>
       </c>
       <c r="D30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E30">
         <v>96.63</v>
@@ -1472,7 +1451,7 @@
         <v>45218</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -1486,7 +1465,7 @@
         <v>67</v>
       </c>
       <c r="D31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E31">
         <v>114.35</v>
@@ -1506,7 +1485,7 @@
         <v>68</v>
       </c>
       <c r="D32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E32">
         <v>111.86</v>
@@ -1951,7 +1930,7 @@
         <v>66</v>
       </c>
       <c r="D58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E58">
         <v>96.88</v>
@@ -1960,7 +1939,7 @@
         <v>45223</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
@@ -1974,7 +1953,7 @@
         <v>67</v>
       </c>
       <c r="D59" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E59">
         <v>106.65</v>
@@ -1994,7 +1973,7 @@
         <v>65</v>
       </c>
       <c r="D60" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E60">
         <v>108</v>
@@ -2439,7 +2418,7 @@
         <v>66</v>
       </c>
       <c r="D86" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E86">
         <v>95.14</v>
@@ -2448,7 +2427,7 @@
         <v>45223</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.45">
@@ -2462,7 +2441,7 @@
         <v>65</v>
       </c>
       <c r="D87" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E87">
         <v>106.07</v>
@@ -2482,7 +2461,7 @@
         <v>67</v>
       </c>
       <c r="D88" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E88">
         <v>105.55</v>
@@ -2927,7 +2906,7 @@
         <v>66</v>
       </c>
       <c r="D114" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E114">
         <v>98.05</v>
@@ -2936,7 +2915,7 @@
         <v>45223</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.45">
@@ -2950,7 +2929,7 @@
         <v>65</v>
       </c>
       <c r="D115" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E115">
         <v>111.86</v>
@@ -2970,7 +2949,7 @@
         <v>67</v>
       </c>
       <c r="D116" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E116">
         <v>112.15</v>
@@ -3415,7 +3394,7 @@
         <v>65</v>
       </c>
       <c r="D142" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E142">
         <v>99</v>
@@ -3424,7 +3403,7 @@
         <v>45223</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.45">
@@ -3438,7 +3417,7 @@
         <v>66</v>
       </c>
       <c r="D143" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E143">
         <v>112.26</v>
@@ -3458,7 +3437,7 @@
         <v>67</v>
       </c>
       <c r="D144" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E144">
         <v>112.91</v>
@@ -3903,7 +3882,7 @@
         <v>66</v>
       </c>
       <c r="D170" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E170">
         <v>97.5</v>
@@ -3912,7 +3891,7 @@
         <v>45223</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.45">
@@ -3926,7 +3905,7 @@
         <v>65</v>
       </c>
       <c r="D171" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E171">
         <v>103.85</v>
@@ -3946,7 +3925,7 @@
         <v>67</v>
       </c>
       <c r="D172" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E172">
         <v>106.07</v>
@@ -4391,7 +4370,7 @@
         <v>66</v>
       </c>
       <c r="D198" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E198">
         <v>96.19</v>
@@ -4400,7 +4379,7 @@
         <v>45223</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.45">
@@ -4414,7 +4393,7 @@
         <v>67</v>
       </c>
       <c r="D199" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E199">
         <v>109.8</v>
@@ -4434,7 +4413,7 @@
         <v>68</v>
       </c>
       <c r="D200" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E200">
         <v>109.42</v>
@@ -4879,7 +4858,7 @@
         <v>66</v>
       </c>
       <c r="D226" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E226">
         <v>91.57</v>
@@ -4888,7 +4867,7 @@
         <v>45223</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.45">
@@ -4902,7 +4881,7 @@
         <v>65</v>
       </c>
       <c r="D227" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E227">
         <v>108</v>
@@ -4922,7 +4901,7 @@
         <v>67</v>
       </c>
       <c r="D228" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E228">
         <v>110.45</v>
@@ -5367,7 +5346,7 @@
         <v>66</v>
       </c>
       <c r="D254" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E254">
         <v>91.29</v>
@@ -5376,7 +5355,7 @@
         <v>45223</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.45">
@@ -5390,7 +5369,7 @@
         <v>65</v>
       </c>
       <c r="D255" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E255">
         <v>106.65</v>
@@ -5410,7 +5389,7 @@
         <v>67</v>
       </c>
       <c r="D256" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E256">
         <v>109.42</v>
@@ -5855,7 +5834,7 @@
         <v>65</v>
       </c>
       <c r="D282" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E282">
         <v>91.57</v>
@@ -5864,7 +5843,7 @@
         <v>45223</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.45">
@@ -5878,7 +5857,7 @@
         <v>66</v>
       </c>
       <c r="D283" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E283">
         <v>106.65</v>
@@ -5898,7 +5877,7 @@
         <v>67</v>
       </c>
       <c r="D284" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E284">
         <v>109.42</v>
@@ -6343,7 +6322,7 @@
         <v>67</v>
       </c>
       <c r="D310" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E310">
         <v>96.43</v>
@@ -6352,7 +6331,7 @@
         <v>45223</v>
       </c>
       <c r="G310" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.45">
@@ -6366,7 +6345,7 @@
         <v>66</v>
       </c>
       <c r="D311" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E311">
         <v>114</v>
@@ -6386,7 +6365,7 @@
         <v>65</v>
       </c>
       <c r="D312" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E312">
         <v>112.5</v>
@@ -6831,7 +6810,7 @@
         <v>67</v>
       </c>
       <c r="D338" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E338">
         <v>96.63</v>
@@ -6840,7 +6819,7 @@
         <v>45223</v>
       </c>
       <c r="G338" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.45">
@@ -6854,7 +6833,7 @@
         <v>68</v>
       </c>
       <c r="D339" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E339">
         <v>106.58</v>
@@ -6874,7 +6853,7 @@
         <v>66</v>
       </c>
       <c r="D340" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E340">
         <v>111.38</v>
@@ -7319,7 +7298,7 @@
         <v>67</v>
       </c>
       <c r="D366" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E366">
         <v>98.36</v>
@@ -7328,7 +7307,7 @@
         <v>45223</v>
       </c>
       <c r="G366" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.45">
@@ -7342,7 +7321,7 @@
         <v>66</v>
       </c>
       <c r="D367" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E367">
         <v>110.08</v>
@@ -7362,7 +7341,7 @@
         <v>68</v>
       </c>
       <c r="D368" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E368">
         <v>112.5</v>
@@ -7807,7 +7786,7 @@
         <v>67</v>
       </c>
       <c r="D394" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E394">
         <v>92.05</v>
@@ -7816,7 +7795,7 @@
         <v>45223</v>
       </c>
       <c r="G394" s="3" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.45">
@@ -7830,7 +7809,7 @@
         <v>66</v>
       </c>
       <c r="D395" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E395">
         <v>108</v>
@@ -7850,7 +7829,7 @@
         <v>65</v>
       </c>
       <c r="D396" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E396">
         <v>112.76</v>
@@ -8295,7 +8274,7 @@
         <v>67</v>
       </c>
       <c r="D422" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E422">
         <v>98.36</v>
@@ -8304,7 +8283,7 @@
         <v>45223</v>
       </c>
       <c r="G422" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.45">
@@ -8318,7 +8297,7 @@
         <v>65</v>
       </c>
       <c r="D423" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E423">
         <v>114</v>
@@ -8338,7 +8317,7 @@
         <v>68</v>
       </c>
       <c r="D424" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E424">
         <v>114.23</v>
@@ -8783,7 +8762,7 @@
         <v>66</v>
       </c>
       <c r="D450" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E450">
         <v>95.85</v>
@@ -8792,7 +8771,7 @@
         <v>45223</v>
       </c>
       <c r="G450" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.45">
@@ -8806,7 +8785,7 @@
         <v>68</v>
       </c>
       <c r="D451" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E451">
         <v>106.65</v>
@@ -8826,7 +8805,7 @@
         <v>67</v>
       </c>
       <c r="D452" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E452">
         <v>108</v>
@@ -9271,7 +9250,7 @@
         <v>66</v>
       </c>
       <c r="D478" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E478">
         <v>96.43</v>
@@ -9280,7 +9259,7 @@
         <v>45223</v>
       </c>
       <c r="G478" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.45">
@@ -9294,7 +9273,7 @@
         <v>67</v>
       </c>
       <c r="D479" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E479">
         <v>109.69</v>
@@ -9314,7 +9293,7 @@
         <v>68</v>
       </c>
       <c r="D480" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E480">
         <v>109.93</v>
@@ -9759,7 +9738,7 @@
         <v>65</v>
       </c>
       <c r="D506" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E506">
         <v>91.8</v>
@@ -9768,7 +9747,7 @@
         <v>45223</v>
       </c>
       <c r="G506" s="3" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.45">
@@ -9782,7 +9761,7 @@
         <v>66</v>
       </c>
       <c r="D507" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E507">
         <v>108</v>
@@ -9802,7 +9781,7 @@
         <v>67</v>
       </c>
       <c r="D508" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E508">
         <v>110.84</v>
@@ -10247,7 +10226,7 @@
         <v>67</v>
       </c>
       <c r="D534" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E534">
         <v>96.88</v>
@@ -10256,7 +10235,7 @@
         <v>45223</v>
       </c>
       <c r="G534" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.45">
@@ -10270,7 +10249,7 @@
         <v>66</v>
       </c>
       <c r="D535" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E535">
         <v>106.65</v>
@@ -10290,7 +10269,7 @@
         <v>65</v>
       </c>
       <c r="D536" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E536">
         <v>111.38</v>
@@ -10735,7 +10714,7 @@
         <v>67</v>
       </c>
       <c r="D562" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E562">
         <v>96</v>
@@ -10744,7 +10723,7 @@
         <v>45223</v>
       </c>
       <c r="G562" s="3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.45">
@@ -10758,7 +10737,7 @@
         <v>66</v>
       </c>
       <c r="D563" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E563">
         <v>114.75</v>
@@ -10778,7 +10757,7 @@
         <v>68</v>
       </c>
       <c r="D564" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E564">
         <v>114</v>
@@ -11223,7 +11202,7 @@
         <v>65</v>
       </c>
       <c r="D590" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E590">
         <v>98.36</v>
@@ -11232,7 +11211,7 @@
         <v>45223</v>
       </c>
       <c r="G590" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.45">
@@ -11246,7 +11225,7 @@
         <v>67</v>
       </c>
       <c r="D591" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E591">
         <v>109.5</v>
@@ -11266,7 +11245,7 @@
         <v>66</v>
       </c>
       <c r="D592" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E592">
         <v>112.5</v>
@@ -11711,7 +11690,7 @@
         <v>65</v>
       </c>
       <c r="D618" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E618">
         <v>94.5</v>
@@ -11720,7 +11699,7 @@
         <v>45351</v>
       </c>
       <c r="G618" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.45">
@@ -11734,7 +11713,7 @@
         <v>66</v>
       </c>
       <c r="D619" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E619">
         <v>112.26</v>
@@ -11754,7 +11733,7 @@
         <v>67</v>
       </c>
       <c r="D620" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E620">
         <v>114.35</v>
@@ -12199,13 +12178,13 @@
         <v>66</v>
       </c>
       <c r="D646" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F646" s="2">
         <v>45351</v>
       </c>
       <c r="G646" s="3" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.45">
@@ -12219,7 +12198,7 @@
         <v>67</v>
       </c>
       <c r="D647" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F647" s="2">
         <v>45351</v>
@@ -12236,7 +12215,7 @@
         <v>68</v>
       </c>
       <c r="D648" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F648" s="2">
         <v>45351</v>
@@ -12678,7 +12657,7 @@
         <v>67</v>
       </c>
       <c r="D674" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E674">
         <v>96.63</v>
@@ -12687,7 +12666,7 @@
         <v>45351</v>
       </c>
       <c r="G674" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.45">
@@ -12701,7 +12680,7 @@
         <v>66</v>
       </c>
       <c r="D675" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E675">
         <v>106.65</v>
@@ -12721,7 +12700,7 @@
         <v>65</v>
       </c>
       <c r="D676" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E676">
         <v>106.65</v>
@@ -13166,7 +13145,7 @@
         <v>67</v>
       </c>
       <c r="D702" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E702">
         <v>93.71</v>
@@ -13175,7 +13154,7 @@
         <v>45351</v>
       </c>
       <c r="G702" s="3" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="703" spans="1:7" x14ac:dyDescent="0.45">
@@ -13189,7 +13168,7 @@
         <v>66</v>
       </c>
       <c r="D703" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E703">
         <v>110.45</v>
@@ -13209,7 +13188,7 @@
         <v>65</v>
       </c>
       <c r="D704" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E704">
         <v>112.26</v>
@@ -13654,7 +13633,7 @@
         <v>66</v>
       </c>
       <c r="D730" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E730">
         <v>94.5</v>
@@ -13663,7 +13642,7 @@
         <v>45351</v>
       </c>
       <c r="G730" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="731" spans="1:7" x14ac:dyDescent="0.45">
@@ -13677,7 +13656,7 @@
         <v>65</v>
       </c>
       <c r="D731" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E731">
         <v>112.5</v>
@@ -13697,7 +13676,7 @@
         <v>67</v>
       </c>
       <c r="D732" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E732">
         <v>113.79</v>
@@ -14142,7 +14121,7 @@
         <v>65</v>
       </c>
       <c r="D758" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="E758">
         <v>96.19</v>
@@ -14151,7 +14130,7 @@
         <v>45351</v>
       </c>
       <c r="G758" s="3" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="759" spans="1:7" x14ac:dyDescent="0.45">
@@ -14165,7 +14144,7 @@
         <v>67</v>
       </c>
       <c r="D759" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="F759" s="2">
         <v>45351</v>
@@ -14182,7 +14161,7 @@
         <v>66</v>
       </c>
       <c r="D760" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E760">
         <v>112.76</v>
@@ -14627,13 +14606,13 @@
         <v>65</v>
       </c>
       <c r="D786" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F786" s="2">
         <v>45351</v>
       </c>
       <c r="G786" s="3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="787" spans="1:7" x14ac:dyDescent="0.45">
@@ -14647,7 +14626,7 @@
         <v>67</v>
       </c>
       <c r="D787" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F787" s="2">
         <v>45351</v>
@@ -14664,7 +14643,7 @@
         <v>68</v>
       </c>
       <c r="D788" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F788" s="2">
         <v>45351</v>
@@ -15106,7 +15085,7 @@
         <v>66</v>
       </c>
       <c r="D814" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E814">
         <v>96.63</v>
@@ -15115,7 +15094,7 @@
         <v>45351</v>
       </c>
       <c r="G814" s="3" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="815" spans="1:7" x14ac:dyDescent="0.45">
@@ -15129,7 +15108,7 @@
         <v>67</v>
       </c>
       <c r="D815" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E815">
         <v>106.65</v>
@@ -15149,7 +15128,7 @@
         <v>68</v>
       </c>
       <c r="D816" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E816">
         <v>106.65</v>
@@ -15594,7 +15573,7 @@
         <v>66</v>
       </c>
       <c r="D842" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E842">
         <v>93.15</v>
@@ -15603,7 +15582,7 @@
         <v>45351</v>
       </c>
       <c r="G842" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="843" spans="1:7" x14ac:dyDescent="0.45">
@@ -15617,7 +15596,7 @@
         <v>65</v>
       </c>
       <c r="D843" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E843">
         <v>109.42</v>
@@ -15637,7 +15616,7 @@
         <v>67</v>
       </c>
       <c r="D844" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E844">
         <v>110.45</v>
@@ -16082,7 +16061,7 @@
         <v>65</v>
       </c>
       <c r="D870" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E870">
         <v>94.5</v>
@@ -16091,7 +16070,7 @@
         <v>45351</v>
       </c>
       <c r="G870" s="3" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="871" spans="1:7" x14ac:dyDescent="0.45">
@@ -16105,7 +16084,7 @@
         <v>66</v>
       </c>
       <c r="D871" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E871">
         <v>112.26</v>
@@ -16125,7 +16104,7 @@
         <v>67</v>
       </c>
       <c r="D872" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E872">
         <v>114.35</v>
@@ -16570,7 +16549,7 @@
         <v>66</v>
       </c>
       <c r="D898" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="E898">
         <v>96.17</v>
@@ -16579,7 +16558,7 @@
         <v>45351</v>
       </c>
       <c r="G898" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="899" spans="1:7" x14ac:dyDescent="0.45">
@@ -16593,7 +16572,7 @@
         <v>67</v>
       </c>
       <c r="D899" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="F899" s="2">
         <v>45351</v>
@@ -16610,7 +16589,7 @@
         <v>65</v>
       </c>
       <c r="D900" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E900">
         <v>112.67</v>
@@ -17055,13 +17034,13 @@
         <v>66</v>
       </c>
       <c r="D926" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F926" s="2">
         <v>45351</v>
       </c>
       <c r="G926" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="927" spans="1:7" x14ac:dyDescent="0.45">
@@ -17075,7 +17054,7 @@
         <v>65</v>
       </c>
       <c r="D927" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F927" s="2">
         <v>45351</v>
@@ -17092,7 +17071,7 @@
         <v>68</v>
       </c>
       <c r="D928" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F928" s="2">
         <v>45351</v>
@@ -17534,7 +17513,7 @@
         <v>67</v>
       </c>
       <c r="D954" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E954">
         <v>96.63</v>
@@ -17543,7 +17522,7 @@
         <v>45351</v>
       </c>
       <c r="G954" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="955" spans="1:7" x14ac:dyDescent="0.45">
@@ -17557,7 +17536,7 @@
         <v>66</v>
       </c>
       <c r="D955" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E955">
         <v>106.65</v>
@@ -17577,7 +17556,7 @@
         <v>68</v>
       </c>
       <c r="D956" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E956">
         <v>106.65</v>
@@ -18022,7 +18001,7 @@
         <v>66</v>
       </c>
       <c r="D982" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E982">
         <v>91.57</v>
@@ -18031,7 +18010,7 @@
         <v>45386</v>
       </c>
       <c r="G982" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="983" spans="1:7" x14ac:dyDescent="0.45">
@@ -18045,7 +18024,7 @@
         <v>65</v>
       </c>
       <c r="D983" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E983">
         <v>108</v>
@@ -18065,7 +18044,7 @@
         <v>67</v>
       </c>
       <c r="D984" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E984">
         <v>111</v>
@@ -18510,7 +18489,7 @@
         <v>66</v>
       </c>
       <c r="D1010" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E1010">
         <v>96.75</v>
@@ -18519,7 +18498,7 @@
         <v>45386</v>
       </c>
       <c r="G1010" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1011" spans="1:7" x14ac:dyDescent="0.45">
@@ -18533,7 +18512,7 @@
         <v>67</v>
       </c>
       <c r="D1011" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E1011">
         <v>111.86</v>
@@ -18553,7 +18532,7 @@
         <v>65</v>
       </c>
       <c r="D1012" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E1012">
         <v>114.35</v>
@@ -18998,7 +18977,7 @@
         <v>65</v>
       </c>
       <c r="D1038" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E1038">
         <v>96.63</v>
@@ -19007,7 +18986,7 @@
         <v>45386</v>
       </c>
       <c r="G1038" s="3" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="1039" spans="1:7" x14ac:dyDescent="0.45">
@@ -19021,7 +19000,7 @@
         <v>67</v>
       </c>
       <c r="D1039" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E1039">
         <v>109.42</v>
@@ -19041,7 +19020,7 @@
         <v>66</v>
       </c>
       <c r="D1040" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E1040">
         <v>112.5</v>
@@ -19486,7 +19465,7 @@
         <v>65</v>
       </c>
       <c r="D1066" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E1066">
         <v>92.57</v>
@@ -19495,7 +19474,7 @@
         <v>45386</v>
       </c>
       <c r="G1066" s="3" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1067" spans="1:7" x14ac:dyDescent="0.45">
@@ -19509,7 +19488,7 @@
         <v>67</v>
       </c>
       <c r="D1067" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E1067">
         <v>111.38</v>
@@ -19529,7 +19508,7 @@
         <v>66</v>
       </c>
       <c r="D1068" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E1068">
         <v>112.91</v>
@@ -19974,13 +19953,13 @@
         <v>65</v>
       </c>
       <c r="D1094" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F1094" s="2">
         <v>45387</v>
       </c>
       <c r="G1094" s="3" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1095" spans="1:7" x14ac:dyDescent="0.45">
@@ -19994,7 +19973,7 @@
         <v>66</v>
       </c>
       <c r="D1095" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F1095" s="2">
         <v>45387</v>
@@ -20011,7 +19990,7 @@
         <v>67</v>
       </c>
       <c r="D1096" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F1096" s="2">
         <v>45387</v>
@@ -20453,13 +20432,13 @@
         <v>66</v>
       </c>
       <c r="D1122" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F1122" s="2">
         <v>45387</v>
       </c>
       <c r="G1122" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1123" spans="1:7" x14ac:dyDescent="0.45">
@@ -20473,7 +20452,7 @@
         <v>65</v>
       </c>
       <c r="D1123" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F1123" s="2">
         <v>45387</v>
@@ -20490,7 +20469,7 @@
         <v>67</v>
       </c>
       <c r="D1124" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F1124" s="2">
         <v>45387</v>
@@ -20932,13 +20911,13 @@
         <v>66</v>
       </c>
       <c r="D1150" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F1150" s="2">
         <v>45387</v>
       </c>
       <c r="G1150" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="1151" spans="1:7" x14ac:dyDescent="0.45">
@@ -20952,7 +20931,7 @@
         <v>67</v>
       </c>
       <c r="D1151" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F1151" s="2">
         <v>45387</v>
@@ -20969,7 +20948,7 @@
         <v>65</v>
       </c>
       <c r="D1152" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F1152" s="2">
         <v>45387</v>
@@ -21411,13 +21390,13 @@
         <v>66</v>
       </c>
       <c r="D1178" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="F1178" s="2">
         <v>45387</v>
       </c>
       <c r="G1178" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="1179" spans="1:7" x14ac:dyDescent="0.45">
@@ -21431,7 +21410,7 @@
         <v>67</v>
       </c>
       <c r="D1179" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F1179" s="2">
         <v>45387</v>
@@ -21448,7 +21427,7 @@
         <v>65</v>
       </c>
       <c r="D1180" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F1180" s="2">
         <v>45387</v>
@@ -21890,13 +21869,13 @@
         <v>66</v>
       </c>
       <c r="D1206" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F1206" s="2">
         <v>45387</v>
       </c>
       <c r="G1206" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1207" spans="1:7" x14ac:dyDescent="0.45">
@@ -21910,7 +21889,7 @@
         <v>65</v>
       </c>
       <c r="D1207" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F1207" s="2">
         <v>45387</v>
@@ -21927,7 +21906,7 @@
         <v>67</v>
       </c>
       <c r="D1208" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F1208" s="2">
         <v>45387</v>
@@ -22369,13 +22348,13 @@
         <v>66</v>
       </c>
       <c r="D1234" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F1234" s="2">
         <v>45387</v>
       </c>
       <c r="G1234" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1235" spans="1:7" x14ac:dyDescent="0.45">
@@ -22389,7 +22368,7 @@
         <v>65</v>
       </c>
       <c r="D1235" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F1235" s="2">
         <v>45387</v>
@@ -22406,7 +22385,7 @@
         <v>67</v>
       </c>
       <c r="D1236" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F1236" s="2">
         <v>45387</v>
@@ -22848,13 +22827,13 @@
         <v>66</v>
       </c>
       <c r="D1262" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F1262" s="2">
         <v>45387</v>
       </c>
       <c r="G1262" s="3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="1263" spans="1:7" x14ac:dyDescent="0.45">
@@ -22868,7 +22847,7 @@
         <v>67</v>
       </c>
       <c r="D1263" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F1263" s="2">
         <v>45387</v>
@@ -22885,7 +22864,7 @@
         <v>65</v>
       </c>
       <c r="D1264" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F1264" s="2">
         <v>45387</v>
@@ -23327,13 +23306,13 @@
         <v>66</v>
       </c>
       <c r="D1290" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F1290" s="2">
         <v>45387</v>
       </c>
       <c r="G1290" s="3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1291" spans="1:7" x14ac:dyDescent="0.45">
@@ -23347,7 +23326,7 @@
         <v>67</v>
       </c>
       <c r="D1291" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F1291" s="2">
         <v>45387</v>
@@ -23364,7 +23343,7 @@
         <v>65</v>
       </c>
       <c r="D1292" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F1292" s="2">
         <v>45387</v>
@@ -23806,13 +23785,13 @@
         <v>67</v>
       </c>
       <c r="D1318" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F1318" s="2">
         <v>45387</v>
       </c>
       <c r="G1318" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="1319" spans="1:7" x14ac:dyDescent="0.45">
@@ -23826,7 +23805,7 @@
         <v>65</v>
       </c>
       <c r="D1319" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F1319" s="2">
         <v>45387</v>
@@ -23843,7 +23822,7 @@
         <v>66</v>
       </c>
       <c r="D1320" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F1320" s="2">
         <v>45387</v>
@@ -24285,13 +24264,13 @@
         <v>66</v>
       </c>
       <c r="D1346" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F1346" s="2">
         <v>45387</v>
       </c>
       <c r="G1346" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="1347" spans="1:7" x14ac:dyDescent="0.45">
@@ -24305,7 +24284,7 @@
         <v>65</v>
       </c>
       <c r="D1347" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F1347" s="2">
         <v>45387</v>
@@ -24322,7 +24301,7 @@
         <v>67</v>
       </c>
       <c r="D1348" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F1348" s="2">
         <v>45387</v>
@@ -24764,13 +24743,13 @@
         <v>67</v>
       </c>
       <c r="D1374" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F1374" s="2">
         <v>45387</v>
       </c>
       <c r="G1374" s="3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="1375" spans="1:7" x14ac:dyDescent="0.45">
@@ -24784,7 +24763,7 @@
         <v>66</v>
       </c>
       <c r="D1375" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F1375" s="2">
         <v>45387</v>
@@ -24801,7 +24780,7 @@
         <v>65</v>
       </c>
       <c r="D1376" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F1376" s="2">
         <v>45387</v>
@@ -25243,13 +25222,13 @@
         <v>65</v>
       </c>
       <c r="D1402" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="F1402" s="2">
         <v>45387</v>
       </c>
       <c r="G1402" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="1403" spans="1:7" x14ac:dyDescent="0.45">
@@ -25263,7 +25242,7 @@
         <v>67</v>
       </c>
       <c r="D1403" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F1403" s="2">
         <v>45387</v>
@@ -25280,7 +25259,7 @@
         <v>66</v>
       </c>
       <c r="D1404" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F1404" s="2">
         <v>45387</v>
@@ -25722,13 +25701,13 @@
         <v>67</v>
       </c>
       <c r="D1430" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F1430" s="2">
         <v>45387</v>
       </c>
       <c r="G1430" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="1431" spans="1:7" x14ac:dyDescent="0.45">
@@ -25742,7 +25721,7 @@
         <v>65</v>
       </c>
       <c r="D1431" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F1431" s="2">
         <v>45387</v>
@@ -25759,7 +25738,7 @@
         <v>68</v>
       </c>
       <c r="D1432" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F1432" s="2">
         <v>45387</v>
@@ -26201,13 +26180,13 @@
         <v>66</v>
       </c>
       <c r="D1458" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F1458" s="2">
         <v>45387</v>
       </c>
       <c r="G1458" s="3" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="1459" spans="1:7" x14ac:dyDescent="0.45">
@@ -26221,7 +26200,7 @@
         <v>65</v>
       </c>
       <c r="D1459" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F1459" s="2">
         <v>45387</v>
@@ -26238,7 +26217,7 @@
         <v>67</v>
       </c>
       <c r="D1460" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F1460" s="2">
         <v>45387</v>
@@ -26680,13 +26659,13 @@
         <v>67</v>
       </c>
       <c r="D1486" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F1486" s="2">
         <v>45387</v>
       </c>
       <c r="G1486" s="3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1487" spans="1:7" x14ac:dyDescent="0.45">
@@ -26700,7 +26679,7 @@
         <v>66</v>
       </c>
       <c r="D1487" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F1487" s="2">
         <v>45387</v>
@@ -26717,7 +26696,7 @@
         <v>65</v>
       </c>
       <c r="D1488" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F1488" s="2">
         <v>45387</v>
@@ -27159,7 +27138,7 @@
         <v>66</v>
       </c>
       <c r="D1514" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E1514">
         <v>95</v>
@@ -27168,7 +27147,7 @@
         <v>45463</v>
       </c>
       <c r="G1514" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1515" spans="1:7" x14ac:dyDescent="0.45">
@@ -27182,7 +27161,7 @@
         <v>65</v>
       </c>
       <c r="D1515" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E1515">
         <v>113</v>
@@ -27202,7 +27181,7 @@
         <v>67</v>
       </c>
       <c r="D1516" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E1516">
         <v>111</v>
@@ -27647,7 +27626,7 @@
         <v>66</v>
       </c>
       <c r="D1542" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E1542">
         <v>97.9</v>
@@ -27656,7 +27635,7 @@
         <v>45463</v>
       </c>
       <c r="G1542" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1543" spans="1:7" x14ac:dyDescent="0.45">
@@ -27670,7 +27649,7 @@
         <v>65</v>
       </c>
       <c r="D1543" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E1543">
         <v>104</v>
@@ -27690,7 +27669,7 @@
         <v>67</v>
       </c>
       <c r="D1544" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E1544">
         <v>110</v>
@@ -28135,7 +28114,7 @@
         <v>66</v>
       </c>
       <c r="D1570" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E1570">
         <v>95</v>
@@ -28144,7 +28123,7 @@
         <v>45484</v>
       </c>
       <c r="G1570" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="1571" spans="1:7" x14ac:dyDescent="0.45">
@@ -28158,7 +28137,7 @@
         <v>67</v>
       </c>
       <c r="D1571" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E1571">
         <v>111</v>
@@ -28178,7 +28157,7 @@
         <v>68</v>
       </c>
       <c r="D1572" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E1572">
         <v>109</v>
@@ -28623,16 +28602,16 @@
         <v>66</v>
       </c>
       <c r="D1598" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E1598" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F1598" s="2">
         <v>45484</v>
       </c>
       <c r="G1598" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="1599" spans="1:7" x14ac:dyDescent="0.45">
@@ -28646,10 +28625,10 @@
         <v>67</v>
       </c>
       <c r="D1599" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="E1599" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F1599" s="2">
         <v>45484</v>
@@ -28666,10 +28645,10 @@
         <v>68</v>
       </c>
       <c r="D1600" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E1600" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F1600" s="2">
         <v>45484</v>
@@ -28686,7 +28665,7 @@
         <v>65</v>
       </c>
       <c r="D1601" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1601">
         <v>0</v>
@@ -28706,7 +28685,7 @@
         <v>69</v>
       </c>
       <c r="D1602" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1602">
         <v>0</v>
@@ -28726,7 +28705,7 @@
         <v>69</v>
       </c>
       <c r="D1603" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1603">
         <v>0</v>
@@ -28746,7 +28725,7 @@
         <v>69</v>
       </c>
       <c r="D1604" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1604">
         <v>0</v>
@@ -28766,7 +28745,7 @@
         <v>69</v>
       </c>
       <c r="D1605" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1605">
         <v>0</v>
@@ -28786,7 +28765,7 @@
         <v>69</v>
       </c>
       <c r="D1606" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1606">
         <v>0</v>
@@ -28806,7 +28785,7 @@
         <v>69</v>
       </c>
       <c r="D1607" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1607">
         <v>0</v>
@@ -28826,7 +28805,7 @@
         <v>69</v>
       </c>
       <c r="D1608" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1608">
         <v>0</v>
@@ -28846,7 +28825,7 @@
         <v>69</v>
       </c>
       <c r="D1609" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1609">
         <v>0</v>
@@ -28866,7 +28845,7 @@
         <v>69</v>
       </c>
       <c r="D1610" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1610">
         <v>0</v>
@@ -28886,7 +28865,7 @@
         <v>69</v>
       </c>
       <c r="D1611" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1611">
         <v>0</v>
@@ -28906,7 +28885,7 @@
         <v>69</v>
       </c>
       <c r="D1612" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1612">
         <v>0</v>
@@ -28926,7 +28905,7 @@
         <v>69</v>
       </c>
       <c r="D1613" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1613">
         <v>0</v>
@@ -28946,7 +28925,7 @@
         <v>69</v>
       </c>
       <c r="D1614" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1614">
         <v>0</v>
@@ -28966,7 +28945,7 @@
         <v>69</v>
       </c>
       <c r="D1615" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1615">
         <v>0</v>
@@ -28986,7 +28965,7 @@
         <v>69</v>
       </c>
       <c r="D1616" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1616">
         <v>0</v>
@@ -29006,7 +28985,7 @@
         <v>69</v>
       </c>
       <c r="D1617" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1617">
         <v>0</v>
@@ -29026,7 +29005,7 @@
         <v>69</v>
       </c>
       <c r="D1618" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1618">
         <v>0</v>
@@ -29046,7 +29025,7 @@
         <v>69</v>
       </c>
       <c r="D1619" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1619">
         <v>0</v>
@@ -29066,7 +29045,7 @@
         <v>69</v>
       </c>
       <c r="D1620" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1620">
         <v>0</v>
@@ -29086,7 +29065,7 @@
         <v>69</v>
       </c>
       <c r="D1621" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1621">
         <v>0</v>
@@ -29106,7 +29085,7 @@
         <v>69</v>
       </c>
       <c r="D1622" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1622">
         <v>0</v>
@@ -29126,7 +29105,7 @@
         <v>69</v>
       </c>
       <c r="D1623" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1623">
         <v>0</v>
@@ -29146,7 +29125,7 @@
         <v>69</v>
       </c>
       <c r="D1624" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1624">
         <v>0</v>
@@ -29166,7 +29145,7 @@
         <v>69</v>
       </c>
       <c r="D1625" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E1625">
         <v>0</v>
@@ -29176,6 +29155,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1625" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="G30" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/pages/video_analysis/WTS_Master_Women.xlsx
+++ b/pages/video_analysis/WTS_Master_Women.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sportnzgroup-my.sharepoint.com/personal/anja_kuys_hpsnz_org_nz/Documents/Desktop/Scripts/CNZPD/pages/video_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{262EE144-5106-46E3-9413-1E8BB520A031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8D09A51-849D-4BFF-9B72-4E1564EF6BF8}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{262EE144-5106-46E3-9413-1E8BB520A031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25C280FD-541B-4B2E-AE68-ACCF94820EC0}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1620" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5737" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5738" uniqueCount="223">
   <si>
     <t>Title</t>
   </si>
@@ -687,6 +687,9 @@
   <si>
     <t>26-07-30 CWG Glasgow NZL Q</t>
   </si>
+  <si>
+    <t>https://youtu.be/-DxHcKVATsM</t>
+  </si>
 </sst>
 </file>
 
@@ -44577,7 +44580,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2513" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2513" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2513" t="s">
         <v>220</v>
       </c>
@@ -44594,7 +44597,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2514" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2514" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2514" t="s">
         <v>220</v>
       </c>
@@ -44611,7 +44614,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2515" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2515" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2515" t="s">
         <v>220</v>
       </c>
@@ -44628,7 +44631,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2516" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2516" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2516" t="s">
         <v>220</v>
       </c>
@@ -44645,7 +44648,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2517" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2517" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2517" t="s">
         <v>220</v>
       </c>
@@ -44662,7 +44665,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2518" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2518" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2518" t="s">
         <v>220</v>
       </c>
@@ -44679,7 +44682,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2519" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2519" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2519" t="s">
         <v>220</v>
       </c>
@@ -44696,7 +44699,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2520" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2520" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2520" t="s">
         <v>220</v>
       </c>
@@ -44713,7 +44716,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2521" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2521" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2521" t="s">
         <v>220</v>
       </c>
@@ -44730,7 +44733,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2522" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2522" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2522" t="s">
         <v>221</v>
       </c>
@@ -44743,8 +44746,11 @@
       <c r="D2522" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="2523" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G2522" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2523" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2523" t="s">
         <v>221</v>
       </c>
@@ -44758,7 +44764,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="2524" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2524" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2524" t="s">
         <v>221</v>
       </c>
@@ -44772,7 +44778,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="2525" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2525" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2525" t="s">
         <v>221</v>
       </c>
@@ -44783,7 +44789,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2526" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2526" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2526" t="s">
         <v>221</v>
       </c>
@@ -44794,7 +44800,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2527" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2527" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2527" t="s">
         <v>221</v>
       </c>
@@ -44805,7 +44811,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2528" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2528" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2528" t="s">
         <v>221</v>
       </c>

--- a/pages/video_analysis/WTS_Master_Women.xlsx
+++ b/pages/video_analysis/WTS_Master_Women.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sportnzgroup-my.sharepoint.com/personal/anja_kuys_hpsnz_org_nz/Documents/Desktop/Scripts/CNZPD/pages/video_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{262EE144-5106-46E3-9413-1E8BB520A031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25C280FD-541B-4B2E-AE68-ACCF94820EC0}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="11_299639D07A829C258C4089D7CCB7B441212EFB98" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F7EADD0-4053-4424-9836-D4ABC2C85345}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5738" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5970" uniqueCount="226">
   <si>
     <t>Title</t>
   </si>
@@ -664,13 +664,25 @@
     <t>https://youtu.be/Nu3NPDPkYww</t>
   </si>
   <si>
+    <t>26-04-17 NC Hong Kong NZL Q</t>
+  </si>
+  <si>
     <t>https://youtu.be/snZ4ShGPdS0</t>
+  </si>
+  <si>
+    <t>26-04-17 NC Hong Kong NZL R1</t>
   </si>
   <si>
     <t>https://youtu.be/O4S4GESjd6Y</t>
   </si>
   <si>
+    <t>26-07-30 CWG Glasgow NZL Q</t>
+  </si>
+  <si>
     <t>Petch</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-DxHcKVATsM</t>
   </si>
   <si>
     <t>Ellesse</t>
@@ -679,32 +691,23 @@
     <t>Liv</t>
   </si>
   <si>
-    <t>26-04-17 NC Hong Kong NZL Q</t>
+    <t>23-03-15 NC CAIRO NZL Q</t>
   </si>
   <si>
-    <t>26-04-17 NC Hong Kong NZL R1</t>
+    <t>23-02-24 NC JAKARTA NZL R1 - tissot</t>
   </si>
   <si>
-    <t>26-07-30 CWG Glasgow NZL Q</t>
-  </si>
-  <si>
-    <t>https://youtu.be/-DxHcKVATsM</t>
+    <t>23-02-24 NC JAKARTA NZL Q - tissot</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1036,16 +1039,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2549"/>
+  <dimension ref="A1:G2633"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.4140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -43777,7 +43778,7 @@
     </row>
     <row r="2466" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2466" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2466">
         <v>6.585</v>
@@ -43792,12 +43793,12 @@
         <v>205</v>
       </c>
       <c r="G2466" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2467" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2467" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2467">
         <v>6.665</v>
@@ -43814,7 +43815,7 @@
     </row>
     <row r="2468" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2468" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2468">
         <v>6.6849999999999996</v>
@@ -43831,7 +43832,7 @@
     </row>
     <row r="2469" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2469" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2469">
         <v>6.7450000000000001</v>
@@ -43848,7 +43849,7 @@
     </row>
     <row r="2470" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2470" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2470">
         <v>14.295999999999999</v>
@@ -43865,7 +43866,7 @@
     </row>
     <row r="2471" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2471" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2471">
         <v>14.576000000000001</v>
@@ -43882,7 +43883,7 @@
     </row>
     <row r="2472" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2472" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2472">
         <v>14.715999999999999</v>
@@ -43899,7 +43900,7 @@
     </row>
     <row r="2473" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2473" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2473">
         <v>18.675999999999998</v>
@@ -43916,7 +43917,7 @@
     </row>
     <row r="2474" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2474" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2474">
         <v>19.015999999999998</v>
@@ -43933,7 +43934,7 @@
     </row>
     <row r="2475" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2475" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2475">
         <v>19.155999999999999</v>
@@ -43950,7 +43951,7 @@
     </row>
     <row r="2476" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2476" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2476">
         <v>22.596</v>
@@ -43967,7 +43968,7 @@
     </row>
     <row r="2477" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2477" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2477">
         <v>22.916</v>
@@ -43984,7 +43985,7 @@
     </row>
     <row r="2478" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2478" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2478">
         <v>23.036000000000001</v>
@@ -44001,7 +44002,7 @@
     </row>
     <row r="2479" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2479" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2479">
         <v>26.498000000000001</v>
@@ -44018,7 +44019,7 @@
     </row>
     <row r="2480" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2480" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2480">
         <v>26.577999999999999</v>
@@ -44035,7 +44036,7 @@
     </row>
     <row r="2481" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2481" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2481">
         <v>26.718</v>
@@ -44052,7 +44053,7 @@
     </row>
     <row r="2482" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2482" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2482">
         <v>30.077999999999999</v>
@@ -44069,7 +44070,7 @@
     </row>
     <row r="2483" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2483" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2483">
         <v>30.218</v>
@@ -44086,7 +44087,7 @@
     </row>
     <row r="2484" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2484" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2484">
         <v>33.578000000000003</v>
@@ -44103,7 +44104,7 @@
     </row>
     <row r="2485" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2485" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2485">
         <v>33.718000000000004</v>
@@ -44120,7 +44121,7 @@
     </row>
     <row r="2486" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2486" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2486">
         <v>37.078000000000003</v>
@@ -44137,7 +44138,7 @@
     </row>
     <row r="2487" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2487" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2487">
         <v>37.238</v>
@@ -44154,7 +44155,7 @@
     </row>
     <row r="2488" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2488" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2488">
         <v>40.658000000000001</v>
@@ -44171,7 +44172,7 @@
     </row>
     <row r="2489" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2489" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2489">
         <v>40.698</v>
@@ -44188,7 +44189,7 @@
     </row>
     <row r="2490" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2490" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2490">
         <v>44.118000000000002</v>
@@ -44205,7 +44206,7 @@
     </row>
     <row r="2491" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2491" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2491">
         <v>47.578000000000003</v>
@@ -44222,7 +44223,7 @@
     </row>
     <row r="2492" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2492" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2492">
         <v>51.078000000000003</v>
@@ -44239,7 +44240,7 @@
     </row>
     <row r="2493" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2493" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B2493">
         <v>54.637999999999998</v>
@@ -44256,7 +44257,7 @@
     </row>
     <row r="2494" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2494" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2494">
         <v>20.504000000000001</v>
@@ -44271,12 +44272,12 @@
         <v>205</v>
       </c>
       <c r="G2494" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2495" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2495" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2495">
         <v>20.603999999999999</v>
@@ -44293,7 +44294,7 @@
     </row>
     <row r="2496" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2496" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2496">
         <v>20.623999999999999</v>
@@ -44310,7 +44311,7 @@
     </row>
     <row r="2497" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2497" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2497">
         <v>20.684000000000001</v>
@@ -44327,7 +44328,7 @@
     </row>
     <row r="2498" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2498" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2498">
         <v>28.248000000000001</v>
@@ -44344,7 +44345,7 @@
     </row>
     <row r="2499" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2499" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2499">
         <v>28.507999999999999</v>
@@ -44361,7 +44362,7 @@
     </row>
     <row r="2500" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2500" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2500">
         <v>28.707999999999998</v>
@@ -44378,7 +44379,7 @@
     </row>
     <row r="2501" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2501" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2501">
         <v>32.619999999999997</v>
@@ -44395,7 +44396,7 @@
     </row>
     <row r="2502" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2502" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2502">
         <v>32.92</v>
@@ -44412,7 +44413,7 @@
     </row>
     <row r="2503" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2503" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2503">
         <v>33.06</v>
@@ -44429,7 +44430,7 @@
     </row>
     <row r="2504" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2504" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2504">
         <v>36.54</v>
@@ -44446,7 +44447,7 @@
     </row>
     <row r="2505" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2505" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2505">
         <v>36.78</v>
@@ -44463,7 +44464,7 @@
     </row>
     <row r="2506" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2506" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2506">
         <v>36.92</v>
@@ -44480,7 +44481,7 @@
     </row>
     <row r="2507" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2507" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2507">
         <v>40.444000000000003</v>
@@ -44497,7 +44498,7 @@
     </row>
     <row r="2508" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2508" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2508">
         <v>40.524000000000001</v>
@@ -44514,7 +44515,7 @@
     </row>
     <row r="2509" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2509" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2509">
         <v>40.643999999999998</v>
@@ -44531,7 +44532,7 @@
     </row>
     <row r="2510" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2510" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2510">
         <v>44.043999999999997</v>
@@ -44548,7 +44549,7 @@
     </row>
     <row r="2511" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2511" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2511">
         <v>44.164000000000001</v>
@@ -44565,7 +44566,7 @@
     </row>
     <row r="2512" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2512" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2512">
         <v>47.543999999999997</v>
@@ -44582,7 +44583,7 @@
     </row>
     <row r="2513" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2513" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2513">
         <v>47.664000000000001</v>
@@ -44599,7 +44600,7 @@
     </row>
     <row r="2514" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2514" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2514">
         <v>51.043999999999997</v>
@@ -44616,7 +44617,7 @@
     </row>
     <row r="2515" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2515" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2515">
         <v>51.183999999999997</v>
@@ -44633,7 +44634,7 @@
     </row>
     <row r="2516" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2516" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2516">
         <v>54.643999999999998</v>
@@ -44650,7 +44651,7 @@
     </row>
     <row r="2517" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2517" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2517">
         <v>54.664000000000001</v>
@@ -44667,7 +44668,7 @@
     </row>
     <row r="2518" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2518" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2518">
         <v>58.103999999999999</v>
@@ -44684,7 +44685,7 @@
     </row>
     <row r="2519" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2519" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2519">
         <v>61.543999999999997</v>
@@ -44701,7 +44702,7 @@
     </row>
     <row r="2520" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2520" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2520">
         <v>65.043999999999997</v>
@@ -44718,7 +44719,7 @@
     </row>
     <row r="2521" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2521" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B2521">
         <v>68.683999999999997</v>
@@ -44735,7 +44736,7 @@
     </row>
     <row r="2522" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2522" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2522">
         <v>15.497</v>
@@ -44744,15 +44745,15 @@
         <v>13</v>
       </c>
       <c r="D2522" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G2522" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2523" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2523" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2523">
         <v>15.497</v>
@@ -44761,12 +44762,12 @@
         <v>15</v>
       </c>
       <c r="D2523" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2524" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2524" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2524">
         <v>15.516999999999999</v>
@@ -44775,12 +44776,12 @@
         <v>8</v>
       </c>
       <c r="D2524" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2525" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2525" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2525">
         <v>15.557</v>
@@ -44791,7 +44792,7 @@
     </row>
     <row r="2526" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2526" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2526">
         <v>22.869</v>
@@ -44802,7 +44803,7 @@
     </row>
     <row r="2527" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2527" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2527">
         <v>23.268999999999998</v>
@@ -44813,7 +44814,7 @@
     </row>
     <row r="2528" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2528" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2528">
         <v>23.449000000000002</v>
@@ -44824,7 +44825,7 @@
     </row>
     <row r="2529" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2529" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2529">
         <v>27.088999999999999</v>
@@ -44835,7 +44836,7 @@
     </row>
     <row r="2530" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2530" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2530">
         <v>27.449000000000002</v>
@@ -44846,7 +44847,7 @@
     </row>
     <row r="2531" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2531" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2531">
         <v>27.689</v>
@@ -44857,7 +44858,7 @@
     </row>
     <row r="2532" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2532" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2532">
         <v>30.809000000000001</v>
@@ -44868,7 +44869,7 @@
     </row>
     <row r="2533" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2533" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2533">
         <v>31.088999999999999</v>
@@ -44879,7 +44880,7 @@
     </row>
     <row r="2534" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2534" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2534">
         <v>31.329000000000001</v>
@@ -44890,7 +44891,7 @@
     </row>
     <row r="2535" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2535" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2535">
         <v>34.429000000000002</v>
@@ -44901,7 +44902,7 @@
     </row>
     <row r="2536" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2536" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2536">
         <v>34.548999999999999</v>
@@ -44912,7 +44913,7 @@
     </row>
     <row r="2537" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2537" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2537">
         <v>34.768999999999998</v>
@@ -44923,7 +44924,7 @@
     </row>
     <row r="2538" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2538" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2538">
         <v>37.988999999999997</v>
@@ -44934,7 +44935,7 @@
     </row>
     <row r="2539" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2539" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2539">
         <v>38.128999999999998</v>
@@ -44945,7 +44946,7 @@
     </row>
     <row r="2540" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2540" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2540">
         <v>41.448999999999998</v>
@@ -44956,7 +44957,7 @@
     </row>
     <row r="2541" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2541" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2541">
         <v>41.569000000000003</v>
@@ -44967,7 +44968,7 @@
     </row>
     <row r="2542" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2542" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2542">
         <v>44.988999999999997</v>
@@ -44978,7 +44979,7 @@
     </row>
     <row r="2543" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2543" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2543">
         <v>45.109000000000002</v>
@@ -44989,7 +44990,7 @@
     </row>
     <row r="2544" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2544" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2544">
         <v>48.689</v>
@@ -44998,9 +44999,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2545" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2545" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2545" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2545">
         <v>48.709000000000003</v>
@@ -45009,9 +45010,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2546" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2546" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2546" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2546">
         <v>52.289000000000001</v>
@@ -45020,9 +45021,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2547" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2547" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2547" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2547">
         <v>55.889000000000003</v>
@@ -45031,9 +45032,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2548" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2548" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2548" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2548">
         <v>59.569000000000003</v>
@@ -45042,9 +45043,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2549" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2549" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2549" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B2549">
         <v>63.320999999999998</v>
@@ -45053,8 +45054,991 @@
         <v>16</v>
       </c>
     </row>
+    <row r="2550" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2550" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2550">
+        <v>8.9860000000000007</v>
+      </c>
+      <c r="C2550" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2550" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2550" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2551" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2551">
+        <v>9.0259999999999998</v>
+      </c>
+      <c r="C2551" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2551" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2551" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2552" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2552" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2552">
+        <v>9.0860000000000003</v>
+      </c>
+      <c r="C2552" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2552" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2552" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2553" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2553" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2553">
+        <v>9.1660000000000004</v>
+      </c>
+      <c r="C2553" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2553" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2553" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2554" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2554" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2554">
+        <v>16.757000000000001</v>
+      </c>
+      <c r="C2554" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2554" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2554" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2555" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2555">
+        <v>17.041</v>
+      </c>
+      <c r="C2555" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2555" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2555" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2556" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2556" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2556">
+        <v>17.100999999999999</v>
+      </c>
+      <c r="C2556" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2556" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2556" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2557" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2557" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2557">
+        <v>21.018999999999998</v>
+      </c>
+      <c r="C2557" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2557" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2557" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2558" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2558" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2558">
+        <v>21.318999999999999</v>
+      </c>
+      <c r="C2558" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2558" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2558" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2559" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2559" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2559">
+        <v>21.459</v>
+      </c>
+      <c r="C2559" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2559" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2559" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2560" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2560" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2560">
+        <v>24.798999999999999</v>
+      </c>
+      <c r="C2560" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2560" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2560" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2561" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2561" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2561">
+        <v>24.978999999999999</v>
+      </c>
+      <c r="C2561" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2561" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2561" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2562" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2562" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2562">
+        <v>25.119</v>
+      </c>
+      <c r="C2562" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2562" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2562" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2563" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2563" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2563">
+        <v>28.459</v>
+      </c>
+      <c r="C2563" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2563" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2563" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2564" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2564" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2564">
+        <v>28.478999999999999</v>
+      </c>
+      <c r="C2564" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2564" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2564" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2565" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2565" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2565">
+        <v>28.599</v>
+      </c>
+      <c r="C2565" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2565" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2565" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2566" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2566" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2566">
+        <v>31.899000000000001</v>
+      </c>
+      <c r="C2566" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2566" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2566" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2567" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2567" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2567">
+        <v>32.018999999999998</v>
+      </c>
+      <c r="C2567" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2567" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2567" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2568" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2568" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2568">
+        <v>35.338999999999999</v>
+      </c>
+      <c r="C2568" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2568" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2568" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2569" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2569" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2569">
+        <v>35.478999999999999</v>
+      </c>
+      <c r="C2569" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2569" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2569" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2570" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2570" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2570">
+        <v>38.838999999999999</v>
+      </c>
+      <c r="C2570" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2570" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2570" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2571" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2571" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2571">
+        <v>38.999000000000002</v>
+      </c>
+      <c r="C2571" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2571" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2571" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2572" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2572" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2572">
+        <v>42.459000000000003</v>
+      </c>
+      <c r="C2572" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2572" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2572" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2573" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2573" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2573">
+        <v>42.539000000000001</v>
+      </c>
+      <c r="C2573" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2573" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2573" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2574" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2574" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2574">
+        <v>45.999000000000002</v>
+      </c>
+      <c r="C2574" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2574" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2574" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2575" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2575" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2575">
+        <v>49.518999999999998</v>
+      </c>
+      <c r="C2575" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2575" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2575" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2576" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2576" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2576">
+        <v>53.134</v>
+      </c>
+      <c r="C2576" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2576" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2576" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2577" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2577" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2577">
+        <v>56.862000000000002</v>
+      </c>
+      <c r="C2577" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2577" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2577" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2578" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2578" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2578" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2578" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2579" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2579" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2579" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2579" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2580" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2580" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2580" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2580" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2581" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2581" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2581" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2581" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2582" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2582" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2582">
+        <v>11.961</v>
+      </c>
+      <c r="C2582" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2583" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2583" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2583" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2584" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2584" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2584" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2585" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2585" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2585" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2586" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2586" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2586" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2587" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2587" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2587" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2588" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2588" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2588" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2589" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2589" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2589" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2590" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2590" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2590" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2591" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2591" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2591">
+        <v>19.388999999999999</v>
+      </c>
+      <c r="C2591" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2592" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2592" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2592" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2593" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2593" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2593" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2594" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2594" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2594" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2595" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2595" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2595" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2596" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2596" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2596">
+        <v>26.285</v>
+      </c>
+      <c r="C2596" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2597" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2597" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2597" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2598" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2598" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2598" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2599" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2599" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2599" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2600" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2600" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2600">
+        <v>33.406999999999996</v>
+      </c>
+      <c r="C2600" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2601" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2601" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2601" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2602" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2602" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2602" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2603" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2603" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2603">
+        <v>40.462000000000003</v>
+      </c>
+      <c r="C2603" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2604" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2604" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2604" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2605" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2605" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2605">
+        <v>47.81</v>
+      </c>
+      <c r="C2605" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2606" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2606" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2606" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2606" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2607" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2607" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2607" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2607" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2608" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2608" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2608" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2608" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2609" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2609" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2609" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2609" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2610" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2610" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2610">
+        <v>12.048999999999999</v>
+      </c>
+      <c r="C2610" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2611" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2611" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2611" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2612" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2612" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2612" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2613" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2613" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2613" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2614" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2614" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2614" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2615" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2615" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2615" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2616" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2616" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2616" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2617" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2617" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2617" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2618" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2618" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2618" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2619" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2619" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2619">
+        <v>19.489999999999998</v>
+      </c>
+      <c r="C2619" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2620" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2620" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2620" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2621" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2621" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2621" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2622" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2622" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2622" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2623" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2623" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2623" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2624" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2624" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2624">
+        <v>26.474</v>
+      </c>
+      <c r="C2624" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2625" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2625" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2625" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2626" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2626" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2626" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2627" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2627" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2627" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2628" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2628" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2628">
+        <v>33.662999999999997</v>
+      </c>
+      <c r="C2628" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2629" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2629" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2629" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2630" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2630" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2630" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2631" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2631" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2631">
+        <v>40.790999999999997</v>
+      </c>
+      <c r="C2631" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2632" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2632" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2632" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2633" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2633" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2633">
+        <v>48.253999999999998</v>
+      </c>
+      <c r="C2633" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="G30" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -45122,14 +46106,9 @@
     <hyperlink ref="G2438" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId65"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G2465 B2514:G2521 B2466:F2466 B2467:G2493 B2494:F2494 B2495:G2495 B2496:G2513" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G2549 B2552:G2577 B2550:G2550 B2551:G2551" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{9d5ca952-e4a5-43e6-b17c-c01d313ad135}" enabled="0" method="" siteId="{9d5ca952-e4a5-43e6-b17c-c01d313ad135}" removed="1"/>
-</clbl:labelList>
 </file>